--- a/data/raw/annual_drivers-SamRodWal.xlsx
+++ b/data/raw/annual_drivers-SamRodWal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rodwals-my.sharepoint.com/personal/samuel_rodwal_com/Documents/Professional_WorkTools/Github/EnergyPricingForecast/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="11_F25DC773A252ABDACC1048DC8198614A5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75894A50-B418-436F-B240-140A4FD6B5D4}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="11_F25DC773A252ABDACC1048DC8198614A5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBE24657-6DA5-46DB-95F7-C89A19779A6D}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="25815" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5595" yWindow="4290" windowWidth="16410" windowHeight="10140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -71,7 +71,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0.0000_);_(&quot;$&quot;* \(#,##0.0000\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.0000_);_(&quot;$&quot;* \(#,##0.0000\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -137,7 +137,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -466,6 +466,21 @@
       <c r="A2">
         <v>2019</v>
       </c>
+      <c r="B2" s="1">
+        <v>10647</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1175</v>
+      </c>
+      <c r="D2" s="2">
+        <v>4911</v>
+      </c>
+      <c r="E2" s="2">
+        <v>2429</v>
+      </c>
+      <c r="F2" s="2">
+        <v>818</v>
+      </c>
       <c r="G2" s="3">
         <v>56.988319999999995</v>
       </c>
@@ -480,6 +495,21 @@
       <c r="A3">
         <v>2020</v>
       </c>
+      <c r="B3" s="1">
+        <v>10115</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1112</v>
+      </c>
+      <c r="D3" s="2">
+        <v>4447</v>
+      </c>
+      <c r="E3" s="2">
+        <v>2700</v>
+      </c>
+      <c r="F3" s="2">
+        <v>707</v>
+      </c>
       <c r="G3" s="3">
         <v>39.16043650793651</v>
       </c>
@@ -494,6 +524,21 @@
       <c r="A4">
         <v>2021</v>
       </c>
+      <c r="B4" s="1">
+        <v>11117</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1140</v>
+      </c>
+      <c r="D4" s="2">
+        <v>4225</v>
+      </c>
+      <c r="E4" s="2">
+        <v>3765</v>
+      </c>
+      <c r="F4" s="2">
+        <v>774</v>
+      </c>
       <c r="G4" s="3">
         <v>68.135099601593637</v>
       </c>
@@ -507,6 +552,21 @@
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2022</v>
+      </c>
+      <c r="B5" s="1">
+        <v>11342</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1037</v>
+      </c>
+      <c r="D5" s="2">
+        <v>4595</v>
+      </c>
+      <c r="E5" s="2">
+        <v>3882</v>
+      </c>
+      <c r="F5" s="2">
+        <v>686</v>
       </c>
       <c r="G5" s="3">
         <v>94.902868525896409</v>
